--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1130,6 +1130,36 @@
         <v>360</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1791933251272</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,8 +1155,40 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
       <c r="H21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1793143612536</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>가스켓</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
         <v>3</v>
       </c>
     </row>

--- a/filter_instock_HOU.xlsx
+++ b/filter_instock_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1187,9 +1187,47 @@
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
       <c r="H22" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1793342008214</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>필터</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>신우</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" t="n">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
